--- a/Demo Summary/Forecast - v1.xlsx
+++ b/Demo Summary/Forecast - v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chenhan/Documents/FDOS/Demo Summary/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89AD248C-02C6-AE41-8D35-8CA7ADE3021A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CF51FA6-BEE4-1D4F-A191-AB03ED45130A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15600" xr2:uid="{00D4898E-51D5-F44F-A983-48A11FF05C41}"/>
   </bookViews>
